--- a/Filtered/HCA__Florida__Westside__Hospital.xlsx
+++ b/Filtered/HCA__Florida__Westside__Hospital.xlsx
@@ -574,6 +574,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -626,6 +636,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -698,6 +718,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -750,6 +780,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -822,6 +862,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -874,6 +924,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -946,6 +1006,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -998,6 +1068,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1070,6 +1150,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1122,6 +1212,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1194,6 +1294,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1266,6 +1376,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1318,6 +1438,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1390,6 +1520,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1442,6 +1582,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1514,6 +1664,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1566,6 +1726,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1638,6 +1808,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1690,6 +1870,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1762,6 +1952,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1814,6 +2014,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1871,6 +2081,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1923,6 +2143,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1995,6 +2225,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2047,6 +2287,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2119,6 +2369,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2171,6 +2431,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2243,6 +2513,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2295,6 +2575,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2367,6 +2657,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2419,6 +2719,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2491,6 +2801,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2543,6 +2863,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2615,6 +2945,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2667,6 +3007,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M36" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2724,6 +3074,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M37" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2776,6 +3136,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M38" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2848,6 +3218,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M39" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2900,6 +3280,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2972,6 +3362,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M41" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3024,6 +3424,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M42" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3096,6 +3506,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M43" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3148,6 +3568,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M44" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3220,6 +3650,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M45" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3272,6 +3712,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M46" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3344,6 +3794,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M47" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3416,6 +3876,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M48" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3468,6 +3938,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M49" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3540,6 +4020,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M50" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3592,6 +4082,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3664,6 +4164,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3716,6 +4226,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M53" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3788,6 +4308,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M54" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3840,6 +4370,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M55" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3912,6 +4452,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M56" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3964,6 +4514,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M57" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4036,6 +4596,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M58" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4088,6 +4658,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M59" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4160,6 +4740,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M60" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4212,6 +4802,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M61" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4284,6 +4884,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M62" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4336,6 +4946,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M63" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4408,6 +5028,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M64" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4480,6 +5110,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M65" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4532,6 +5172,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M66" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4604,6 +5254,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M67" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4656,6 +5316,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M68" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4713,6 +5383,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M69" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4765,6 +5445,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M70" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4837,6 +5527,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M71" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4889,6 +5589,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M72" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4961,6 +5671,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M73" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5013,6 +5733,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M74" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5085,6 +5815,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M75" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5137,6 +5877,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M76" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5209,6 +5959,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M77" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5261,6 +6021,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M78" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5333,6 +6103,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M79" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5385,6 +6165,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M80" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5457,6 +6247,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M81" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5509,6 +6309,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M82" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5581,6 +6391,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M83" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5633,6 +6453,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M84" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5705,6 +6535,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M85" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5757,6 +6597,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M86" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5829,6 +6679,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M87" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5881,6 +6741,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M88" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5938,6 +6808,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M89" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5990,6 +6870,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M90" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6062,6 +6952,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M91" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6114,6 +7014,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M92" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6186,6 +7096,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M93" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6238,6 +7158,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M94" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6310,6 +7240,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M95" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6362,6 +7302,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M96" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6434,6 +7384,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M97" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6486,6 +7446,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M98" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6558,6 +7528,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M99" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6610,6 +7590,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M100" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6682,6 +7672,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M101" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6734,6 +7734,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M102" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6806,6 +7816,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M103" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6858,6 +7878,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M104" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6930,6 +7960,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M105" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6982,6 +8022,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M106" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7054,6 +8104,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M107" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7106,6 +8166,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M108" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7178,6 +8248,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M109" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7230,6 +8310,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M110" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7302,6 +8392,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M111" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7374,6 +8474,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M112" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7426,6 +8536,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M113" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7498,6 +8618,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M114" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7570,6 +8700,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M115" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7622,6 +8762,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M116" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7694,6 +8844,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M117" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7746,6 +8906,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M118" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7818,6 +8988,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M119" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7890,6 +9070,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M120" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7942,6 +9132,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M121" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8014,6 +9214,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M122" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8066,6 +9276,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M123" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8138,6 +9358,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M124" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8210,6 +9440,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M125" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8262,6 +9502,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M126" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8334,6 +9584,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M127" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8386,6 +9646,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M128" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8458,6 +9728,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M129" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8510,6 +9790,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M130" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8582,6 +9872,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M131" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8634,6 +9934,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M132" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8691,6 +10001,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M133" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8743,6 +10063,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M134" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8800,6 +10130,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M135" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8857,6 +10197,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M136" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8909,6 +10259,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M137" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8981,6 +10341,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M138" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9033,6 +10403,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M139" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9105,6 +10485,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M140" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9157,6 +10547,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M141" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9229,6 +10629,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M142" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9281,6 +10691,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M143" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9353,6 +10773,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M144" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9405,6 +10835,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M145" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9477,6 +10917,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M146" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9529,6 +10979,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M147" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9601,6 +11061,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M148" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9653,6 +11123,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M149" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9725,6 +11205,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M150" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9777,6 +11267,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M151" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9849,6 +11349,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M152" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9901,6 +11411,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M153" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9973,6 +11493,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M154" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10025,6 +11555,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M155" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10097,6 +11637,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M156" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10149,6 +11699,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M157" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10221,6 +11781,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M158" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10273,6 +11843,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M159" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10345,6 +11925,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M160" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10397,6 +11987,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M161" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10469,6 +12069,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M162" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10521,6 +12131,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M163" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10593,6 +12213,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M164" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10645,6 +12275,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M165" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10717,6 +12357,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M166" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10789,6 +12439,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M167" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10841,6 +12501,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M168" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10898,6 +12568,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M169" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10950,6 +12630,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M170" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11022,6 +12712,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M171" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11074,6 +12774,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M172" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11146,6 +12856,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M173" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11198,6 +12918,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M174" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11270,6 +13000,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M175" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11322,6 +13062,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M176" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11394,6 +13144,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M177" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11446,6 +13206,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M178" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11518,6 +13288,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M179" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11570,6 +13350,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M180" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11642,6 +13432,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M181" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11694,6 +13494,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M182" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11766,6 +13576,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M183" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11818,6 +13638,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M184" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11890,6 +13720,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M185" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11942,6 +13782,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M186" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12014,6 +13864,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M187" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12066,6 +13926,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M188" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12138,6 +14008,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M189" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12190,6 +14070,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M190" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12262,6 +14152,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M191" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12314,6 +14214,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M192" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12386,6 +14296,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M193" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12438,6 +14358,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M194" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12510,6 +14440,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M195" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12562,6 +14502,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M196" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12634,6 +14584,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M197" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12686,6 +14646,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M198" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12758,6 +14728,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M199" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12810,6 +14790,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M200" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12882,6 +14872,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M201" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12934,6 +14934,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M202" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13006,6 +15016,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M203" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13058,6 +15078,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M204" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13130,6 +15160,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M205" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13182,6 +15222,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M206" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13254,6 +15304,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M207" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13306,6 +15366,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M208" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13378,6 +15448,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M209" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13430,6 +15510,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M210" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13502,6 +15592,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M211" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13554,6 +15654,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M212" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13626,6 +15736,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M213" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13678,6 +15798,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M214" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13750,6 +15880,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M215" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13802,6 +15942,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M216" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13874,6 +16024,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M217" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13926,6 +16086,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M218" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13998,6 +16168,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M219" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14050,6 +16230,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M220" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14122,6 +16312,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M221" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14174,6 +16374,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M222" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14246,6 +16456,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M223" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14298,6 +16518,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M224" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14370,6 +16600,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M225" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14422,6 +16662,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M226" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14479,6 +16729,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M227" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14531,6 +16791,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M228" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14603,6 +16873,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M229" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14655,6 +16935,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M230" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14727,6 +17017,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M231" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14779,6 +17079,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M232" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14851,6 +17161,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M233" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14903,6 +17223,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M234" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14975,6 +17305,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M235" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15027,6 +17367,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M236" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15099,6 +17449,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M237" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15151,6 +17511,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M238" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15223,6 +17593,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M239" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15295,6 +17675,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M240" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15347,6 +17737,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M241" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15419,6 +17819,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M242" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15471,6 +17881,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M243" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15543,6 +17963,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M244" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15595,6 +18025,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M245" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15667,6 +18107,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M246" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15719,6 +18169,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M247" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15791,6 +18251,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M248" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15843,6 +18313,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M249" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15915,6 +18395,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M250" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15967,6 +18457,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M251" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16039,6 +18539,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M252" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16091,6 +18601,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M253" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16163,6 +18683,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M254" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16215,6 +18745,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M255" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16287,6 +18827,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M256" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16339,6 +18889,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M257" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16411,6 +18971,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M258" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16463,6 +19033,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M259" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16535,6 +19115,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M260" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16587,6 +19177,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M261" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16659,6 +19259,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M262" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16711,6 +19321,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M263" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16783,6 +19403,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M264" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16835,6 +19465,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M265" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16907,6 +19547,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M266" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16959,6 +19609,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M267" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17031,6 +19691,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M268" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17083,6 +19753,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M269" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17155,6 +19835,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M270" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17207,6 +19897,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M271" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17279,6 +19979,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M272" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17331,6 +20041,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M273" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17403,6 +20123,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M274" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17455,6 +20185,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M275" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17527,6 +20267,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M276" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17579,6 +20329,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M277" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17651,6 +20411,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M278" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17703,6 +20473,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M279" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17775,6 +20555,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M280" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17827,6 +20617,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M281" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17899,6 +20699,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M282" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17951,6 +20761,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M283" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18023,6 +20843,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M284" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18075,6 +20905,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M285" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18147,6 +20987,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M286" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18199,6 +21049,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M287" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18271,6 +21131,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M288" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18323,6 +21193,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M289" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18395,6 +21275,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M290" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18467,6 +21357,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M291" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18519,6 +21419,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M292" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18591,6 +21501,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M293" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18643,6 +21563,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M294" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18715,6 +21645,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M295" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18767,6 +21707,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M296" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18839,6 +21789,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M297" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18891,6 +21851,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M298" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18963,6 +21933,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M299" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19035,6 +22015,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M300" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19087,6 +22077,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M301" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19159,6 +22159,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M302" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19211,6 +22221,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M303" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19283,6 +22303,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M304" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19355,6 +22385,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M305" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19407,6 +22447,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M306" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19479,6 +22529,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M307" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19531,6 +22591,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M308" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19603,6 +22673,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M309" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19655,6 +22735,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M310" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19712,6 +22802,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M311" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19764,6 +22864,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M312" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19836,6 +22946,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M313" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19888,6 +23008,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M314" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19960,6 +23090,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M315" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20012,6 +23152,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M316" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20084,6 +23234,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M317" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20136,6 +23296,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M318" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20193,6 +23363,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M319" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20245,6 +23425,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M320" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20317,6 +23507,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M321" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20369,6 +23569,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M322" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20441,6 +23651,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M323" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20493,6 +23713,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M324" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20565,6 +23795,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M325" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20617,6 +23857,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M326" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20689,6 +23939,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M327" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20741,6 +24001,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M328" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20813,6 +24083,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M329" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20865,6 +24145,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M330" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20937,6 +24227,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M331" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20989,6 +24289,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M332" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21061,6 +24371,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M333" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21113,6 +24433,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M334" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21170,6 +24500,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M335" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21222,6 +24562,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M336" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21294,6 +24644,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M337" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21346,6 +24706,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M338" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21418,6 +24788,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M339" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21470,6 +24850,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M340" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21542,6 +24932,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M341" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21594,6 +24994,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M342" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21666,6 +25076,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M343" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21718,6 +25138,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M344" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21790,6 +25220,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M345" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21842,6 +25282,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M346" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21914,6 +25364,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M347" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21966,6 +25426,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M348" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22038,6 +25508,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M349" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22090,6 +25570,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M350" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22162,6 +25652,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M351" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22214,6 +25714,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M352" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22286,6 +25796,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M353" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22338,6 +25858,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M354" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22410,6 +25940,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M355" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22462,6 +26002,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M356" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22534,6 +26084,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M357" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22586,6 +26146,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M358" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22658,6 +26228,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M359" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22710,6 +26290,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M360" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22782,6 +26372,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M361" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22834,6 +26434,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M362" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22906,6 +26516,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M363" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22958,6 +26578,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M364" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23015,6 +26645,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M365" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23072,6 +26712,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M366" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23129,6 +26779,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M367" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23181,6 +26841,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M368" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23253,6 +26923,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M369" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23305,6 +26985,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M370" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23362,6 +27052,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M371" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23419,6 +27119,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M372" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23476,6 +27186,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M373" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23533,6 +27253,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M374" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23590,6 +27320,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M375" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23642,6 +27382,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M376" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23714,6 +27464,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M377" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23766,6 +27526,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M378" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23823,6 +27593,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M379" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23880,6 +27660,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M380" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23932,6 +27722,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M381" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24004,6 +27804,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M382" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24056,6 +27866,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M383" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24113,6 +27933,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M384" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24165,6 +27995,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M385" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24222,6 +28062,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M386" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24279,6 +28129,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M387" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24331,6 +28191,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M388" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24388,6 +28258,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M389" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24445,6 +28325,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M390" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24502,6 +28392,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M391" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24554,6 +28454,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M392" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24611,6 +28521,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M393" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24668,6 +28588,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M394" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24725,6 +28655,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M395" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24777,6 +28717,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M396" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24834,6 +28784,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M397" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24891,6 +28851,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M398" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24948,6 +28918,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M399" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25000,6 +28980,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M400" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25072,6 +29062,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M401" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25124,6 +29124,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M402" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25181,6 +29191,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M403" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25233,6 +29253,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M404" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25305,6 +29335,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M405" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25357,6 +29397,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M406" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25414,6 +29464,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M407" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25471,6 +29531,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M408" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25528,6 +29598,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M409" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25580,6 +29660,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M410" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25652,6 +29742,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M411" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25704,6 +29804,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M412" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25761,6 +29871,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M413" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25818,6 +29938,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M414" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25870,6 +30000,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M415" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25927,6 +30067,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M416" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25984,6 +30134,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M417" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26041,6 +30201,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M418" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26091,6 +30261,16 @@
       <c r="J419" t="inlineStr">
         <is>
           <t>Acute</t>
+        </is>
+      </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>COCWS</t>
+        </is>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
         </is>
       </c>
       <c r="M419" t="inlineStr">
